--- a/社地址.xlsx
+++ b/社地址.xlsx
@@ -944,7 +944,7 @@
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>週一、三、五上午0830~1200</t>
+          <t>週一至週五上午0830~1200</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1450,7 +1450,7 @@
       <c r="E19" s="14" t="n"/>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>每週一及每週二 14::00-17:30</t>
+          <t>每週一及每週二 14:00-17:30</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -1588,7 +1588,7 @@
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>週一、三9:00-12:00, 13:00-16:00</t>
+          <t>週三9:00-12:00, 13:00-16:00</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1994,7 +1994,7 @@
       <c r="E31" s="14" t="n"/>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>週一,週三晚間07：00-10：00 週二,週四,週五上午08：00-11：00,下午13：00-18：00</t>
+          <t>週一,週三晚間07：00-10：00 週二,週四,週五上午08：30-11：30,下午13：00-18：00</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
